--- a/data/precios_creatina_500.xlsx
+++ b/data/precios_creatina_500.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -60,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -489,7 +486,7 @@
       <c r="E2" t="n">
         <v>14.04</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="2" t="n">
         <v>46144</v>
       </c>
     </row>
@@ -515,7 +512,7 @@
       <c r="E3" t="n">
         <v>14.04</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="2" t="n">
         <v>46144</v>
       </c>
     </row>
@@ -541,13 +538,13 @@
       <c r="E4" t="n">
         <v>14.04</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="2" t="n">
         <v>46144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46144.71278268509</v>
+        <v>46144.71278268519</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
